--- a/data/trans_dic/P1435_2011_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1435_2011_2023-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,51</t>
+          <t>0,97; 3,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,91</t>
+          <t>2,03; 7,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 12,45</t>
+          <t>7,19; 12,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,26</t>
+          <t>0,96; 3,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,07</t>
+          <t>4,33; 6,87</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,81</t>
+          <t>0,22; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,4</t>
+          <t>1,03; 3,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,47</t>
+          <t>1,8; 6,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,43</t>
+          <t>6,71; 11,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,36</t>
+          <t>1,06; 3,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,39</t>
+          <t>4,0; 6,57</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,66</t>
+          <t>0,17; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,88</t>
+          <t>0,34; 2,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,17</t>
+          <t>0,73; 4,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 12,66</t>
+          <t>5,83; 12,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,93</t>
+          <t>0,46; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,91</t>
+          <t>2,24; 4,58</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,31</t>
+          <t>0,91; 2,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,04</t>
+          <t>2,71; 5,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 61,55</t>
+          <t>7,3; 10,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,43</t>
+          <t>1,18; 2,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 43,56</t>
+          <t>3,86; 5,45</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,54</t>
+          <t>1,34; 4,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,47</t>
+          <t>2,54; 5,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 12,11</t>
+          <t>8,44; 11,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,53</t>
+          <t>1,6; 3,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,68</t>
+          <t>5,82; 8,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1037,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,43</t>
+          <t>2,32; 4,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,72</t>
+          <t>5,81; 9,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,69</t>
+          <t>1,78; 3,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,33</t>
+          <t>4,69; 7,59</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,53</t>
+          <t>0,17; 0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,19</t>
+          <t>1,28; 2,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,22</t>
+          <t>2,96; 4,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 32,76</t>
+          <t>8,05; 9,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,36</t>
+          <t>1,66; 2,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 18,48</t>
+          <t>4,86; 5,82</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42640</t>
+          <t>45889</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>56593</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 5437</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5204; 17754</t>
+          <t>5344; 17794</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6269; 21737</t>
+          <t>6372; 22724</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32956; 55692</t>
+          <t>35077; 59453</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6474; 24520</t>
+          <t>7210; 23376</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41786; 67370</t>
+          <t>44916; 71338</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41856</t>
+          <t>46205</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>928; 7565</t>
+          <t>908; 7731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4389; 15390</t>
+          <t>4991; 17517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5929; 21860</t>
+          <t>6099; 21195</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24834; 43558</t>
+          <t>28305; 47533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8165; 25408</t>
+          <t>8040; 25973</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31867; 53255</t>
+          <t>36225; 59491</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>21299</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1056; 10477</t>
+          <t>1046; 10360</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>867; 12501</t>
+          <t>1604; 11301</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1927; 10840</t>
+          <t>1906; 10764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10023; 21137</t>
+          <t>10935; 23970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4133; 17129</t>
+          <t>4125; 16316</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7599; 32591</t>
+          <t>14720; 30109</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271334</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>286468</t>
+          <t>91994</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5758</t>
+          <t>0; 4850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8841; 23877</t>
+          <t>10289; 24662</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23218; 46318</t>
+          <t>20805; 44277</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79438; 601838</t>
+          <t>62865; 89493</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22610; 46794</t>
+          <t>22633; 46417</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84996; 876719</t>
+          <t>76830; 108633</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79564</t>
+          <t>82593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>96080</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7268</t>
+          <t>0; 7071</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6727; 21518</t>
+          <t>7591; 23334</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20805; 41673</t>
+          <t>19353; 41009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59831; 101502</t>
+          <t>70037; 98941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21558; 44912</t>
+          <t>20328; 43792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73716; 113864</t>
+          <t>81207; 114622</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53412</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>65184</t>
         </is>
       </c>
     </row>
@@ -1939,27 +1939,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 18613</t>
+          <t>0; 17564</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24438; 49175</t>
+          <t>25687; 50003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42851; 66239</t>
+          <t>48954; 77973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25908; 50825</t>
+          <t>24546; 49207</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44764; 73295</t>
+          <t>50689; 82000</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>54751</t>
+          <t>57838</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>494971</t>
+          <t>319517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>549722</t>
+          <t>377355</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5900; 18270</t>
+          <t>5950; 18847</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40226; 73775</t>
+          <t>44093; 75997</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104114; 149956</t>
+          <t>104907; 149967</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>297723; 1169974</t>
+          <t>292320; 350914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>116396; 164616</t>
+          <t>115621; 163953</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>341317; 1283709</t>
+          <t>343913; 411744</t>
         </is>
       </c>
     </row>
